--- a/data/营销信息.xlsx
+++ b/data/营销信息.xlsx
@@ -501,21 +501,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M47"/>
-  <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" customWidth="1"/>
-    <col min="13" max="13" width="10.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3072,7 +3057,7 @@
         <v>应急订单安排</v>
       </c>
       <c r="B2" t="str">
-        <v>2026年8月18日-8月21日</v>
+        <v>2026-08-18</v>
       </c>
       <c r="C2" t="str">
         <v>2026年7月-8月</v>
@@ -3084,7 +3069,7 @@
         <v>参加相关活动的客户下午4点前</v>
       </c>
       <c r="F2" t="str">
-        <v>当天下午4点</v>
+        <v>2026-08-18</v>
       </c>
       <c r="G2" t="str">
         <v xml:space="preserve"> 8月18日兑付1、3批次（其中3批次为当天批次）；8月19日兑付2、4批次（其中4批次为当天批次）；8月20日兑付5批次（当天批次）。具体兑付明细如表。</v>
@@ -3097,7 +3082,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
   </ignoredErrors>
